--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -664,9 +664,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -674,9 +674,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -709,9 +709,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -719,9 +719,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -733,9 +733,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -743,9 +743,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -788,9 +788,9 @@
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>E</t>
@@ -799,9 +799,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>2,elec</t>
@@ -1086,108 +1086,106 @@
   </numFmts>
   <fonts count="61" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1198,299 +1196,292 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3" tint="9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2594,9 +2585,8 @@
         <vertAlign val="baseline"/>
         <sz val="9"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -2616,11 +2606,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2640,11 +2629,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2664,11 +2652,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2688,11 +2675,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2712,11 +2698,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2736,11 +2721,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2760,11 +2744,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2784,11 +2767,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2808,11 +2790,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2832,11 +2813,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2856,11 +2836,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2880,11 +2859,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2904,11 +2882,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2928,11 +2905,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2952,11 +2928,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2976,11 +2951,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3000,11 +2974,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3024,11 +2997,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3048,11 +3020,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3072,11 +3043,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3096,11 +3066,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3120,11 +3089,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3144,11 +3112,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3168,11 +3135,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3192,11 +3158,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3216,11 +3181,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3240,11 +3204,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3264,11 +3227,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3288,11 +3250,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3312,11 +3273,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3336,11 +3296,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3360,11 +3319,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3384,11 +3342,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3408,11 +3365,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3432,11 +3388,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3456,11 +3411,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3480,11 +3434,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3790,7 +3743,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3798,14 +3751,14 @@
             <a:t>14.1.1 Purchased electricity -</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0" baseline="0">
+            <a:rPr lang="en-AU" sz="1200" b="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
             </a:rPr>
             <a:t> location-based</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1400" b="0">
+          <a:endParaRPr lang="en-AU" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3877,17 +3830,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B377A225-5B38-4F4F-8E60-34C9F7D0C552}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Location-based Scope 2 emissions from purchased electricity</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3948,7 +3901,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:schemeClr val="accent5">
                   <a:lumMod val="75000"/>
@@ -4026,19 +3979,19 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{C2E10899-E275-4A32-9FFF-C3F12CBDD2AA}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="accent5">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Market-based Scope 2 emissions from purchased electricity</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:schemeClr val="accent5">
                 <a:lumMod val="50000"/>
@@ -4113,14 +4066,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4128,13 +4081,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶𝐻</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>4</m:t>
@@ -4142,7 +4095,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4152,14 +4105,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑗</m:t>
@@ -4172,14 +4125,14 @@
                             <m:chr m:val="∑"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑘</m:t>
@@ -4192,14 +4145,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑚</m:t>
@@ -4212,14 +4165,14 @@
                                     <m:chr m:val="∑"/>
                                     <m:supHide m:val="on"/>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:naryPr>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑇</m:t>
@@ -4230,7 +4183,7 @@
                                     <m:d>
                                       <m:dPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
@@ -4239,14 +4192,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝐷</m:t>
@@ -4254,7 +4207,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -4262,7 +4215,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -4270,14 +4223,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑀</m:t>
@@ -4285,7 +4238,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘𝑚𝑇</m:t>
@@ -4293,7 +4246,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -4301,14 +4254,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑁</m:t>
@@ -4316,7 +4269,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -4334,7 +4287,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -4342,14 +4295,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -4357,7 +4310,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -4367,7 +4320,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4415,12 +4368,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶𝐻4=∑8_𝑗▒∑8_𝑘▒∑8_𝑚▒∑8_𝑇▒(𝐷_𝑗𝑘×𝑀_𝑗𝑘𝑚𝑇×𝑁_𝑗𝑘 ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4486,14 +4439,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4501,13 +4454,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -4515,7 +4468,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4523,14 +4476,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑄</m:t>
@@ -4538,7 +4491,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -4546,13 +4499,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐸</m:t>
@@ -4560,14 +4513,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -4575,13 +4528,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -4589,7 +4542,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -4597,14 +4550,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -4612,7 +4565,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -4622,7 +4575,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4670,12 +4623,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_(2,𝑒𝑙𝑒𝑐)=𝑄_𝑒𝑙𝑒𝑐×𝐸𝐹_(2,𝑒𝑙𝑒𝑐)×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4741,14 +4694,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4756,13 +4709,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -4770,7 +4723,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4778,7 +4731,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -4787,14 +4740,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑄</m:t>
@@ -4802,7 +4755,7 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -4810,7 +4763,7 @@
                           </m:sub>
                         </m:sSub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>×</m:t>
@@ -4818,14 +4771,14 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:dPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>1−</m:t>
@@ -4833,26 +4786,26 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑃𝑃</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>+</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐽𝑅𝑃𝑃</m:t>
@@ -4862,7 +4815,7 @@
                           </m:e>
                         </m:d>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−</m:t>
@@ -4870,7 +4823,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -4879,14 +4832,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝐸</m:t>
@@ -4894,14 +4847,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶</m:t>
@@ -4909,7 +4862,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑠𝑢𝑟𝑟𝑒𝑛𝑑𝑒𝑟𝑒𝑑</m:t>
@@ -4917,13 +4870,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>−</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝐸</m:t>
@@ -4931,14 +4884,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶</m:t>
@@ -4946,7 +4899,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜𝑛𝑠𝑖𝑡𝑒</m:t>
@@ -4956,7 +4909,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4964,14 +4917,14 @@
                             <m:sSup>
                               <m:sSupPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSupPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>10</m:t>
@@ -4979,7 +4932,7 @@
                               </m:e>
                               <m:sup>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>3</m:t>
@@ -4991,13 +4944,13 @@
                       </m:e>
                     </m:d>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐸</m:t>
@@ -5005,14 +4958,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5020,19 +4973,19 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑅𝑀𝐹</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -5040,7 +4993,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -5048,14 +5001,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -5063,7 +5016,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -5073,7 +5026,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5122,12 +5075,12 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_(2,𝑒𝑙𝑒𝑐)=(𝑄_𝑒𝑙𝑒𝑐×(1−(𝑅𝑃𝑃+𝐽𝑅𝑃𝑃))−((𝑅𝐸𝐶_𝑠𝑢𝑟𝑟𝑒𝑛𝑑𝑒𝑟𝑒𝑑−𝑅𝐸𝐶_𝑜𝑛𝑠𝑖𝑡𝑒 )×10^3 ))×𝐸𝐹_(𝑅𝑀𝐹2,𝑒𝑙𝑒𝑐)×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5194,7 +5147,7 @@
                       <m:rPr>
                         <m:sty m:val="p"/>
                       </m:rPr>
-                      <a:rPr lang="en-AU" sz="1100" b="0" i="1">
+                      <a:rPr lang="en-AU" sz="1000" b="0" i="1">
                         <a:solidFill>
                           <a:srgbClr val="C00000"/>
                         </a:solidFill>
@@ -5203,7 +5156,7 @@
                       <m:t>ORIGINAL</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" b="0" i="1">
+                      <a:rPr lang="en-AU" sz="1000" b="0" i="1">
                         <a:solidFill>
                           <a:srgbClr val="C00000"/>
                         </a:solidFill>
@@ -5214,14 +5167,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -5229,13 +5182,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -5243,7 +5196,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -5251,7 +5204,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -5260,14 +5213,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑄</m:t>
@@ -5275,7 +5228,7 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -5283,7 +5236,7 @@
                           </m:sub>
                         </m:sSub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>×</m:t>
@@ -5291,14 +5244,14 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:dPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>1−</m:t>
@@ -5306,26 +5259,26 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑃𝑃</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>+</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐽𝑅𝑃𝑃</m:t>
@@ -5335,7 +5288,7 @@
                           </m:e>
                         </m:d>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−</m:t>
@@ -5343,7 +5296,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -5352,14 +5305,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝐸</m:t>
@@ -5367,14 +5320,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶</m:t>
@@ -5382,7 +5335,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑠𝑢𝑟𝑟𝑒𝑛𝑑𝑒𝑟𝑒𝑑</m:t>
@@ -5390,13 +5343,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>−</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝐸</m:t>
@@ -5404,14 +5357,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶</m:t>
@@ -5419,7 +5372,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜𝑛𝑠𝑖𝑡𝑒</m:t>
@@ -5429,7 +5382,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -5437,14 +5390,14 @@
                             <m:sSup>
                               <m:sSupPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSupPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>10</m:t>
@@ -5452,7 +5405,7 @@
                               </m:e>
                               <m:sup>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>−3</m:t>
@@ -5464,13 +5417,13 @@
                       </m:e>
                     </m:d>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐸</m:t>
@@ -5478,14 +5431,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5493,19 +5446,19 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑅𝑀𝐹</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑙𝑒𝑐</m:t>
@@ -5513,7 +5466,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -5521,14 +5474,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -5536,7 +5489,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -5546,7 +5499,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5595,7 +5548,7 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" b="0" i="0">
+                <a:rPr lang="en-AU" sz="1000" b="0" i="0">
                   <a:solidFill>
                     <a:srgbClr val="C00000"/>
                   </a:solidFill>
@@ -5604,12 +5557,12 @@
                 <a:t>ORIGINAL: </a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_(2,𝑒𝑙𝑒𝑐)=(𝑄_𝑒𝑙𝑒𝑐×(1−(𝑅𝑃𝑃+𝐽𝑅𝑃𝑃))−((𝑅𝐸𝐶_𝑠𝑢𝑟𝑟𝑒𝑛𝑑𝑒𝑟𝑒𝑑−𝑅𝐸𝐶_𝑜𝑛𝑠𝑖𝑡𝑒 )×10^(−3) ))×𝐸𝐹_(𝑅𝑀𝐹2,𝑒𝑙𝑒𝑐)×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -6355,12 +6308,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -6571,31 +6524,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="120" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="119" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="14" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -6612,7 +6565,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -6642,7 +6595,7 @@
       <c r="O1" s="53"/>
       <c r="P1" s="53"/>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
       <c r="E2" s="53"/>
@@ -6659,7 +6612,7 @@
       <c r="P2" s="53"/>
       <c r="Q2" s="54"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6679,13 +6632,13 @@
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6705,7 +6658,7 @@
       <c r="N5" s="36"/>
       <c r="O5" s="33"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="56" t="s">
         <v>83</v>
       </c>
@@ -6721,32 +6674,32 @@
       <c r="N6" s="35"/>
       <c r="O6" s="34"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -6755,53 +6708,53 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:23" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="W45" t="s">
         <v>81</v>
       </c>
@@ -6819,7 +6772,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:H87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -6837,10 +6790,10 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6852,7 +6805,7 @@
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -6866,7 +6819,7 @@
       <c r="G4" s="19"/>
       <c r="H4" s="20"/>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6878,7 +6831,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="18"/>
       <c r="D6" s="17" t="s">
         <v>79</v>
@@ -6888,7 +6841,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
@@ -6896,7 +6849,7 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
@@ -6915,7 +6868,7 @@
       </c>
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -6937,7 +6890,7 @@
       </c>
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
@@ -6959,7 +6912,7 @@
       </c>
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="18"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -6967,7 +6920,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="18"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -6975,7 +6928,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
@@ -6986,7 +6939,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -6998,7 +6951,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="18"/>
       <c r="D15" s="1"/>
       <c r="E15" s="40"/>
@@ -7006,7 +6959,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="18"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -7014,7 +6967,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
@@ -7025,7 +6978,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
@@ -7037,7 +6990,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -7049,7 +7002,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="18"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -7057,7 +7010,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="18"/>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="18"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -7065,7 +7018,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="18"/>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="18"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -7073,7 +7026,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="18"/>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="18"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -7081,7 +7034,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="18"/>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="18"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -7089,7 +7042,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="18"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -7097,7 +7050,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="18"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -7105,7 +7058,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="18"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -7113,7 +7066,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="18"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -7121,7 +7074,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="18"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -7129,7 +7082,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="18"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -7137,7 +7090,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="18"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -7145,7 +7098,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="18"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -7153,7 +7106,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="18"/>
     </row>
-    <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="18"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -7161,7 +7114,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="18"/>
     </row>
-    <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="18"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7169,7 +7122,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="18"/>
     </row>
-    <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="18"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -7177,7 +7130,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="18"/>
     </row>
-    <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="18"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -7185,7 +7138,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="18"/>
     </row>
-    <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="18"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -7193,7 +7146,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="18"/>
     </row>
-    <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="18"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -7201,7 +7154,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="18"/>
     </row>
-    <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="18"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -7209,7 +7162,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="18"/>
     </row>
-    <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="18"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -7217,7 +7170,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="18"/>
     </row>
-    <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="18"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -7225,7 +7178,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
-    <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="18"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -7233,7 +7186,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
-    <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="18"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -7241,7 +7194,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
-    <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="18"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -7249,7 +7202,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
-    <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="18"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -7257,7 +7210,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
-    <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="18"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -7265,7 +7218,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
-    <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="18"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -7273,7 +7226,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
-    <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="18"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -7281,7 +7234,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
-    <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="18"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -7289,7 +7242,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
-    <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="18"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -7297,7 +7250,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
-    <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="18"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -7305,7 +7258,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="18"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -7313,7 +7266,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="18"/>
     </row>
-    <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="18"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -7321,7 +7274,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="18"/>
     </row>
-    <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="18"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -7329,7 +7282,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="18"/>
     </row>
-    <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="18"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -7337,7 +7290,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="18"/>
     </row>
-    <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="18"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -7345,7 +7298,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="18"/>
     </row>
-    <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="18"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -7353,7 +7306,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="18"/>
     </row>
-    <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="18"/>
       <c r="D58" s="1"/>
       <c r="E58" s="24"/>
@@ -7361,7 +7314,7 @@
       <c r="G58" s="18"/>
       <c r="H58" s="18"/>
     </row>
-    <row r="59" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="18"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -7369,7 +7322,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="18"/>
     </row>
-    <row r="60" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="18"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -7377,7 +7330,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="18"/>
     </row>
-    <row r="61" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="18"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -7385,7 +7338,7 @@
       <c r="G61" s="1"/>
       <c r="H61" s="18"/>
     </row>
-    <row r="62" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="18"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -7393,7 +7346,7 @@
       <c r="G62" s="1"/>
       <c r="H62" s="18"/>
     </row>
-    <row r="63" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="18"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -7401,7 +7354,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="18"/>
     </row>
-    <row r="64" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="18"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -7409,7 +7362,7 @@
       <c r="G64" s="1"/>
       <c r="H64" s="18"/>
     </row>
-    <row r="65" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="18"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -7417,7 +7370,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="18"/>
     </row>
-    <row r="66" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="18"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -7425,7 +7378,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="18"/>
     </row>
-    <row r="67" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="18"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -7433,7 +7386,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="18"/>
     </row>
-    <row r="68" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="18"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -7441,7 +7394,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="18"/>
     </row>
-    <row r="69" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="18"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -7449,7 +7402,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="18"/>
     </row>
-    <row r="70" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="18"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -7457,7 +7410,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="18"/>
     </row>
-    <row r="71" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="18"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -7465,7 +7418,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="18"/>
     </row>
-    <row r="72" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="18"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -7473,7 +7426,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="18"/>
     </row>
-    <row r="73" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="18"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -7481,7 +7434,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="18"/>
     </row>
-    <row r="74" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="18"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7489,7 +7442,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="18"/>
     </row>
-    <row r="75" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="18"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -7497,7 +7450,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="18"/>
     </row>
-    <row r="76" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="18"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -7505,7 +7458,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="18"/>
     </row>
-    <row r="77" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="18"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -7513,7 +7466,7 @@
       <c r="G77" s="1"/>
       <c r="H77" s="18"/>
     </row>
-    <row r="78" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="18"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -7521,7 +7474,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="18"/>
     </row>
-    <row r="79" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="18"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -7529,7 +7482,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="18"/>
     </row>
-    <row r="80" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="18"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -7537,7 +7490,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="18"/>
     </row>
-    <row r="81" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="18"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -7545,7 +7498,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="18"/>
     </row>
-    <row r="82" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="18"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -7553,7 +7506,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="18"/>
     </row>
-    <row r="83" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="18"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -7561,7 +7514,7 @@
       <c r="G83" s="1"/>
       <c r="H83" s="18"/>
     </row>
-    <row r="84" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="18"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -7569,7 +7522,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="18"/>
     </row>
-    <row r="85" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="18"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -7577,7 +7530,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="18"/>
     </row>
-    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
       <c r="E86" s="18"/>
@@ -7585,7 +7538,7 @@
       <c r="G86" s="18"/>
       <c r="H86" s="18"/>
     </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="18"/>
       <c r="D87" s="18"/>
       <c r="E87" s="18"/>
@@ -7604,7 +7557,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AA160"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="7" customWidth="1"/>
@@ -7625,7 +7578,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -7636,7 +7589,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -7663,7 +7616,7 @@
       <c r="W3" s="10"/>
       <c r="X3" s="10"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -7678,7 +7631,7 @@
       <c r="J4" s="64"/>
       <c r="K4" s="64"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -7688,12 +7641,12 @@
       </c>
       <c r="N5" s="65"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="66"/>
       <c r="N6" s="67"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="1" t="s">
         <v>96</v>
@@ -7703,7 +7656,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
@@ -7714,14 +7667,14 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
       <c r="N9" s="70"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
@@ -7734,11 +7687,11 @@
       <c r="G10" s="61"/>
       <c r="N10" s="70"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="N11" s="73"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="69" t="s">
         <v>101</v>
@@ -7750,7 +7703,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
@@ -7767,7 +7720,7 @@
       <c r="N13" s="76"/>
       <c r="O13" s="76"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -7775,12 +7728,12 @@
       <c r="N14" s="76"/>
       <c r="O14" s="76"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="N15" s="76"/>
       <c r="O15" s="76"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="D16" s="6" t="s">
         <v>105</v>
@@ -7788,12 +7741,12 @@
       <c r="N16" s="76"/>
       <c r="O16" s="76"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
@@ -7805,7 +7758,7 @@
       <c r="F18" s="36"/>
       <c r="G18" s="33"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -7818,14 +7771,14 @@
       <c r="G19" s="34"/>
       <c r="N19" s="65"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="1"/>
       <c r="E20" s="78"/>
       <c r="F20" s="2"/>
       <c r="N20" s="67"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>108</v>
@@ -7837,7 +7790,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="1" t="s">
         <v>110</v>
@@ -7850,29 +7803,29 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="67"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="G30" s="79"/>
       <c r="L30" s="80"/>
@@ -7890,7 +7843,7 @@
       <c r="X30" s="80"/>
       <c r="Y30" s="80"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="G31" s="78"/>
       <c r="L31" s="81"/>
@@ -7908,7 +7861,7 @@
       <c r="X31" s="81"/>
       <c r="Y31" s="81"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="G32" s="78"/>
       <c r="L32" s="81"/>
@@ -7926,7 +7879,7 @@
       <c r="X32" s="81"/>
       <c r="Y32" s="81"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="G33" s="82"/>
       <c r="L33" s="81"/>
@@ -7944,7 +7897,7 @@
       <c r="X33" s="81"/>
       <c r="Y33" s="81"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="83"/>
       <c r="K34" s="84"/>
@@ -7963,7 +7916,7 @@
       <c r="X34" s="81"/>
       <c r="Y34" s="81"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="83"/>
       <c r="K35" s="84"/>
@@ -7982,7 +7935,7 @@
       <c r="X35" s="81"/>
       <c r="Y35" s="81"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="85"/>
       <c r="E36" s="85"/>
@@ -8007,7 +7960,7 @@
       <c r="X36" s="81"/>
       <c r="Y36" s="81"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="85"/>
       <c r="E37" s="85"/>
@@ -8032,7 +7985,7 @@
       <c r="X37" s="81"/>
       <c r="Y37" s="81"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="85"/>
       <c r="E38" s="85"/>
@@ -8057,7 +8010,7 @@
       <c r="X38" s="81"/>
       <c r="Y38" s="81"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="85"/>
       <c r="E39" s="85"/>
@@ -8082,7 +8035,7 @@
       <c r="X39" s="81"/>
       <c r="Y39" s="81"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="88"/>
       <c r="E40" s="88"/>
@@ -8107,27 +8060,27 @@
       <c r="X40" s="91"/>
       <c r="Y40" s="91"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="92"/>
       <c r="E47" s="92"/>
@@ -8135,7 +8088,7 @@
       <c r="G47" s="92"/>
       <c r="H47" s="92"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="93"/>
       <c r="E48" s="93"/>
@@ -8143,7 +8096,7 @@
       <c r="G48" s="94"/>
       <c r="H48" s="93"/>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="93"/>
       <c r="E49" s="93"/>
@@ -8151,7 +8104,7 @@
       <c r="G49" s="94"/>
       <c r="H49" s="93"/>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="93"/>
       <c r="E50" s="93"/>
@@ -8159,7 +8112,7 @@
       <c r="G50" s="94"/>
       <c r="H50" s="93"/>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="95"/>
       <c r="E51" s="96"/>
@@ -8167,76 +8120,76 @@
       <c r="G51" s="96"/>
       <c r="H51" s="97"/>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="G54" s="98"/>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="17"/>
       <c r="F57" s="99"/>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="1"/>
       <c r="E58" s="100"/>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="1"/>
       <c r="E59" s="100"/>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="1"/>
       <c r="E60" s="101"/>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="17"/>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="1"/>
       <c r="E64" s="100"/>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="1"/>
       <c r="E65" s="100"/>
     </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="1"/>
       <c r="E66" s="101"/>
     </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="102"/>
       <c r="E69" s="102"/>
@@ -8245,7 +8198,7 @@
       <c r="H69" s="102"/>
       <c r="I69" s="102"/>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="102"/>
       <c r="E70" s="102"/>
@@ -8254,7 +8207,7 @@
       <c r="H70" s="102"/>
       <c r="I70" s="102"/>
     </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="102"/>
       <c r="E71" s="102"/>
@@ -8263,7 +8216,7 @@
       <c r="H71" s="102"/>
       <c r="I71" s="102"/>
     </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="102"/>
       <c r="E72" s="102"/>
@@ -8272,273 +8225,273 @@
       <c r="H72" s="102"/>
       <c r="I72" s="102"/>
     </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="D78" s="103"/>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="D79" s="103"/>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="D80" s="103"/>
     </row>
-    <row r="81" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="103"/>
     </row>
-    <row r="82" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="103"/>
     </row>
-    <row r="83" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A160"/>
     </row>
   </sheetData>
@@ -8563,7 +8516,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:L365"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -8584,10 +8537,10 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -8601,13 +8554,13 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -8622,14 +8575,14 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="38" t="str">
         <f>IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "Complete the fields in the Location-based section", "Complete the fields in the Market-based section")</f>
         <v>Complete the fields in the Location-based section</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
@@ -8642,7 +8595,7 @@
       <c r="I8" s="105"/>
       <c r="J8" s="105"/>
     </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -8651,19 +8604,19 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="59" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
@@ -8673,7 +8626,7 @@
       <c r="E13" s="61"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -8682,7 +8635,7 @@
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="s">
         <v>88</v>
       </c>
@@ -8693,7 +8646,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="s">
         <v>90</v>
       </c>
@@ -8703,7 +8656,7 @@
       </c>
       <c r="F16" s="18"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
@@ -8717,19 +8670,19 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="105"/>
       <c r="D20" s="105"/>
       <c r="E20" s="105"/>
@@ -8739,18 +8692,18 @@
       <c r="I20" s="105"/>
       <c r="J20" s="105"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E22" s="38" t="str">
         <f>IF(E16="ACT", "", "ALERT: Your farm is not in the ACT, so the JRPP is not applicable")</f>
         <v>ALERT: Your farm is not in the ACT, so the JRPP is not applicable</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
         <v>128</v>
       </c>
@@ -8761,7 +8714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
         <v>118</v>
       </c>
@@ -8772,7 +8725,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>120</v>
       </c>
@@ -8783,8 +8736,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
         <v>127</v>
       </c>
@@ -8795,8 +8748,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
         <v>141</v>
       </c>
@@ -8806,7 +8759,7 @@
       </c>
       <c r="K29" s="47"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="1" t="s">
         <v>126</v>
       </c>
@@ -8816,27 +8769,27 @@
       </c>
       <c r="K30" s="47"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K31" s="47"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="59" t="s">
         <v>125</v>
       </c>
       <c r="K32" s="47"/>
     </row>
-    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K33" s="47"/>
     </row>
-    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="60" t="s">
         <v>149</v>
       </c>
       <c r="E34" s="61"/>
       <c r="K34" s="47"/>
     </row>
-    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="110" t="s">
         <v>122</v>
       </c>
@@ -8857,7 +8810,7 @@
       </c>
       <c r="L36" s="47"/>
     </row>
-    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="26" t="s">
         <v>153</v>
       </c>
@@ -8880,7 +8833,7 @@
       </c>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="26" t="s">
         <v>150</v>
       </c>
@@ -8902,7 +8855,7 @@
         <v>Elegible</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="26" t="s">
         <v>151</v>
       </c>
@@ -8924,7 +8877,7 @@
         <v>Elegible</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="47" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="47" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -8935,7 +8888,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:12" s="47" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="47" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
@@ -8956,18 +8909,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="46"/>
     </row>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="46"/>
       <c r="D43" s="59" t="s">
         <v>129</v>
       </c>
       <c r="J43" s="46"/>
     </row>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="110" t="s">
         <v>122</v>
       </c>
@@ -8987,7 +8940,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="26" t="s">
         <v>140</v>
       </c>
@@ -9010,7 +8963,7 @@
         <v>Ineligible - outside reporting year</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="26" t="s">
         <v>152</v>
       </c>
@@ -9033,7 +8986,7 @@
         <v>Elegible</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="118">
         <v>45597</v>
       </c>
@@ -9056,8 +9009,8 @@
         <v>Elegible</v>
       </c>
     </row>
-    <row r="49" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
         <v>144</v>
       </c>
@@ -9069,126 +9022,126 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="109"/>
     </row>
-    <row r="56" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="109"/>
     </row>
-    <row r="57" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D365" s="38"/>
     </row>
   </sheetData>
@@ -9315,7 +9268,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:K342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -9333,10 +9286,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -9353,13 +9306,13 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -9369,19 +9322,19 @@
         <v>Location-based Scope 2 emissions from purchased electricity</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">Electricity_Equations.VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Source()</f>
         <v>VEERG 2026: 14.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="31" t="str" cm="1">
         <f t="array" ref="D7">Electricity_Equations.VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Variation()</f>
         <v>Added g variable to capture which grid electricity was purchased from</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
@@ -9393,19 +9346,19 @@
         <v>=Electricity_Equations.VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="29" t="s">
         <v>12</v>
       </c>
@@ -9414,7 +9367,7 @@
         <v>E_2elec</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="29" t="s">
         <v>4</v>
       </c>
@@ -9423,12 +9376,12 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="116" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -9454,7 +9407,7 @@
       </c>
       <c r="J14" s="49"/>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="48" t="str">
         <v>EF_2elec</v>
       </c>
@@ -9474,7 +9427,7 @@
       </c>
       <c r="J15" s="49"/>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="48" t="str">
         <v>g</v>
       </c>
@@ -9494,12 +9447,12 @@
       </c>
       <c r="J16" s="49"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
@@ -9516,14 +9469,14 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="105"/>
       <c r="D21" s="105"/>
       <c r="E21" s="105"/>
@@ -9534,25 +9487,25 @@
       <c r="J21" s="105"/>
       <c r="K21" s="105"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="6" t="str" cm="1">
         <f t="array" ref="D22">Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissions_Title()</f>
         <v>Market-based Scope 2 emissions from purchased electricity</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="5" t="str" cm="1">
         <f t="array" ref="D23">Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissions_Source()</f>
         <v>VEERG 2026: 14.1.2, Equation (1)</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="31" t="str" cm="1">
         <f t="array" ref="D24">Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissions_Variation()</f>
         <v>VARIATION ON SOURCE: In order to convert megawatt hours to kilowatt hours, the REC_surrendered and REC_onsite variables are multiplied by 10^3 instead of 10^-3.</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="11" t="s">
         <v>9</v>
       </c>
@@ -9561,9 +9514,9 @@
         <v>=Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="29" t="s">
         <v>12</v>
       </c>
@@ -9572,7 +9525,7 @@
         <v>E_2elec</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="29" t="s">
         <v>4</v>
       </c>
@@ -9581,8 +9534,8 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="48" t="str" cm="1">
         <f t="array" ref="D31:E37">_xlfn.CHOOSECOLS(Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissions_Arguments(),1,2)</f>
         <v>Q_elec</v>
@@ -9604,7 +9557,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="48" t="str">
         <v>RPP</v>
       </c>
@@ -9624,7 +9577,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="48" t="str">
         <v>JRPP</v>
       </c>
@@ -9644,7 +9597,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="48" t="str">
         <v>REC_surrendered</v>
       </c>
@@ -9664,7 +9617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="48" t="str">
         <v>REC_onsite</v>
       </c>
@@ -9684,7 +9637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="48" t="str">
         <v>EF_RMF2elec</v>
       </c>
@@ -9704,7 +9657,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="48" t="str">
         <v>i</v>
       </c>
@@ -9724,8 +9677,8 @@
         <v>Western Australia</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="104" t="s">
         <v>116</v>
       </c>
@@ -9738,248 +9691,248 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H40" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E44" s="46"/>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="18"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="18"/>
     </row>
   </sheetData>
@@ -9998,7 +9951,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AI165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -10025,13 +9978,13 @@
       <c r="AH1"/>
       <c r="AI1"/>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="AG2"/>
       <c r="AH2"/>
       <c r="AI2"/>
     </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -10067,13 +10020,13 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
     </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -10083,7 +10036,7 @@
         <v>Electricity scope 2 and scope 3 location-based emission factors</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Source()</f>
         <v>Australian National Greenhouse Accounts Factors 2025 - Table 1</v>
@@ -10091,7 +10044,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
     </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="31" t="str" cm="1">
         <f t="array" ref="D7">"⚠️" &amp; Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: NSW and ACT split into separate rows.</v>
@@ -10099,7 +10052,7 @@
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
     </row>
-    <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
@@ -10107,7 +10060,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -10122,7 +10075,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
         <v>Electricity</v>
@@ -10140,7 +10093,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data(), Table_SourceData_ElectricityEFs[[#Headers],[State, Territory or grid description]], 0)</f>
         <v>ACT</v>
@@ -10154,7 +10107,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data(), Table_SourceData_ElectricityEFs[[#Headers],[State, Territory or grid description]], 0)</f>
         <v>Victoria</v>
@@ -10168,7 +10121,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
@@ -10185,7 +10138,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="str">
         <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
         <v>14.1.1-2 Purchased electricity</v>
@@ -10203,7 +10156,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" t="str" cm="1">
         <f t="array" ref="D15">Common_InputFunctions.Utility_DisplayArrayInTable(Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data(), Table_SourceData_ElectricityEFs[[#Headers],[State, Territory or grid description]], 0)</f>
         <v>Western Australia - South West Interconnected System (SWIS)</v>
@@ -10217,7 +10170,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" t="str" cm="1">
         <f t="array" ref="D16">Common_InputFunctions.Utility_DisplayArrayInTable(Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data(), Table_SourceData_ElectricityEFs[[#Headers],[State, Territory or grid description]], 0)</f>
         <v>Western Australia - North Western Interconnected System (NWIS)</v>
@@ -10231,7 +10184,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119" t="s">
         <v>1</v>
       </c>
@@ -10248,7 +10201,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57" t="str">
         <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
         <v>Constants - Electricity</v>
@@ -10266,7 +10219,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -10284,21 +10237,21 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="6" t="str" cm="1">
         <f t="array" ref="D21">Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Title()</f>
         <v>Electricity scope 2 and scope 3 market-based emission factors</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="5" t="str" cm="1">
         <f t="array" ref="D22">Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Source()</f>
         <v>Australian National Greenhouse Accounts Factors 2025 - Table 2a</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="115" t="s">
         <v>113</v>
       </c>
@@ -10315,7 +10268,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Data(), Table_SourceData_ElectricityEFsMarketBased[[#Headers],[State, Territory or grid description]], 0)</f>
         <v>National</v>
@@ -10337,146 +10290,146 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10493,7 +10446,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="7" customWidth="1"/>
@@ -10526,10 +10479,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -10556,11 +10509,11 @@
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="3"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -10568,7 +10521,7 @@
       </c>
       <c r="BM5" s="3"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="119" t="s">
         <v>1</v>
       </c>
@@ -10582,7 +10535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -10600,7 +10553,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -10618,7 +10571,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="26" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10633,7 +10586,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="26" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10648,7 +10601,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="26" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10664,7 +10617,7 @@
       </c>
       <c r="BM11" s="3"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="26" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10680,7 +10633,7 @@
       </c>
       <c r="BM12" s="3"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="26" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10695,7 +10648,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="26" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10710,129 +10663,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="6" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="5" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="26" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="26" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="26" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="26" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="26" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="26" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="26" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="26" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="26" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="26" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="6" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="5" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="26" t="s">
         <v>10</v>
@@ -10841,7 +10794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="26" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10852,7 +10805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="26" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10863,7 +10816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="26" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10874,7 +10827,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="26" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10885,7 +10838,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="26" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10896,7 +10849,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="26" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10907,7 +10860,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="26" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10918,24 +10871,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="6" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="5" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="26" t="s">
         <v>10</v>
@@ -10953,7 +10906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="26" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10976,7 +10929,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="26" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10999,7 +10952,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="26" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -11022,7 +10975,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="26" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -11045,7 +10998,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="26" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -11068,7 +11021,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="26" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -11091,7 +11044,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="26" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -11114,49 +11067,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="6" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="5" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="31" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="31" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="31" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="26" t="s">
         <v>3</v>
@@ -11165,7 +11118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="26" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11176,7 +11129,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="26" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11187,7 +11140,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="26" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11198,7 +11151,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="26" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11209,7 +11162,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="26" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11220,7 +11173,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="26" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11231,7 +11184,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="26" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11242,7 +11195,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="26" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11253,7 +11206,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="26" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11264,7 +11217,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="26" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11275,7 +11228,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="26" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11286,7 +11239,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="26" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11297,7 +11250,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="26" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11308,7 +11261,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="26" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -11319,64 +11272,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="6" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="5" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="31" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="31" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="31" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="31" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="31" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="26" t="s">
         <v>3</v>
@@ -11428,7 +11381,7 @@
       </c>
       <c r="T89" s="26"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="26" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11496,7 +11449,7 @@
       </c>
       <c r="T90" s="26"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="26" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11564,7 +11517,7 @@
       </c>
       <c r="T91" s="26"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="26" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11632,7 +11585,7 @@
       </c>
       <c r="T92" s="26"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="26" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11700,7 +11653,7 @@
       </c>
       <c r="T93" s="26"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="26" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11768,7 +11721,7 @@
       </c>
       <c r="T94" s="26"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="26" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11836,7 +11789,7 @@
       </c>
       <c r="T95" s="26"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="26" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11904,7 +11857,7 @@
       </c>
       <c r="T96" s="26"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="26" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11972,66 +11925,66 @@
       </c>
       <c r="T97" s="26"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="30" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="30" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="30" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="30" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="30"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="6" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="5" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="31" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="26" t="s">
         <v>35</v>
@@ -12046,7 +11999,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="26" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -12065,7 +12018,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="26" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -12084,7 +12037,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="26" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -12103,13 +12056,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="6" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -12117,7 +12070,7 @@
       </c>
       <c r="BN115" s="7"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="5" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -12125,7 +12078,7 @@
       </c>
       <c r="BN116" s="7"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="31" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -12133,11 +12086,11 @@
       </c>
       <c r="BN117" s="7"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="7"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="26" t="s">
         <v>38</v>
@@ -12153,7 +12106,7 @@
       </c>
       <c r="BN119" s="7"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="26" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -12173,7 +12126,7 @@
       </c>
       <c r="BN120" s="7"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="26" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -12193,31 +12146,31 @@
       </c>
       <c r="BN121" s="7"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="7"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="6" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="5" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="26" t="s">
         <v>40</v>
@@ -12226,7 +12179,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="26" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -12237,7 +12190,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="26" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -12248,13 +12201,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="6" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -12262,7 +12215,7 @@
       </c>
       <c r="E132" s="18"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="5" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -12270,7 +12223,7 @@
       </c>
       <c r="E133" s="18"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>46</v>
@@ -12279,7 +12232,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -12290,7 +12243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -12301,10 +12254,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="7"/>
       <c r="BO138" s="7"/>
@@ -12319,7 +12272,7 @@
       <c r="BX138" s="7"/>
       <c r="BY138" s="7"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="6" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -12338,7 +12291,7 @@
       <c r="BX139" s="7"/>
       <c r="BY139" s="7"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="5" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -12357,7 +12310,7 @@
       <c r="BX140" s="7"/>
       <c r="BY140" s="7"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="31" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -12365,7 +12318,7 @@
       </c>
       <c r="BN141" s="7"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="26" t="s">
         <v>56</v>
@@ -12375,7 +12328,7 @@
       </c>
       <c r="BN142" s="7"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="26" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -12387,7 +12340,7 @@
       </c>
       <c r="BN143" s="7"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -12399,7 +12352,7 @@
       </c>
       <c r="BN144" s="7"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -12411,7 +12364,7 @@
       </c>
       <c r="BN145" s="7"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -12423,7 +12376,7 @@
       </c>
       <c r="BN146" s="7"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -12435,15 +12388,15 @@
       </c>
       <c r="BN147" s="7"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="7"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="7"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="6" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -12451,7 +12404,7 @@
       </c>
       <c r="BN150" s="7"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="5" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -12459,11 +12412,11 @@
       </c>
       <c r="BN151" s="7"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="7"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="26" t="s">
         <v>42</v>
@@ -12483,7 +12436,7 @@
       <c r="BL153" s="3"/>
       <c r="BM153" s="3"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="26" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12505,7 +12458,7 @@
       <c r="BL154" s="3"/>
       <c r="BM154" s="3"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="26" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12527,7 +12480,7 @@
       <c r="BL155" s="3"/>
       <c r="BM155" s="3"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="26" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12538,7 +12491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="26" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12549,7 +12502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="26" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12560,34 +12513,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="6" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="18"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="5" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="18"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="5" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="18"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="18" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -12596,17 +12549,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="7"/>
       <c r="BO165" s="7"/>
       <c r="BP165" s="7"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="7"/>
       <c r="BO166" s="7"/>
       <c r="BP166" s="7"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="6" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -12615,7 +12568,7 @@
       <c r="BO167" s="7"/>
       <c r="BP167" s="7"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="5" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -12624,7 +12577,7 @@
       <c r="BO168" s="7"/>
       <c r="BP168" s="7"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="5" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -12633,7 +12586,7 @@
       <c r="BO169" s="7"/>
       <c r="BP169" s="7"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -12645,17 +12598,17 @@
       <c r="BO170" s="7"/>
       <c r="BP170" s="7"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="7"/>
       <c r="BO171" s="7"/>
       <c r="BP171" s="7"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="7"/>
       <c r="BO172" s="7"/>
       <c r="BP172" s="7"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="6" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -12664,7 +12617,7 @@
       <c r="BO173" s="7"/>
       <c r="BP173" s="7"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="5" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -12673,7 +12626,7 @@
       <c r="BO174" s="7"/>
       <c r="BP174" s="7"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -12686,17 +12639,17 @@
       <c r="BO175" s="7"/>
       <c r="BP175" s="7"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="7"/>
       <c r="BO176" s="7"/>
       <c r="BP176" s="7"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="7"/>
       <c r="BO177" s="7"/>
       <c r="BP177" s="7"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="6" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -12705,7 +12658,7 @@
       <c r="BO178" s="7"/>
       <c r="BP178" s="7"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="5" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -12714,39 +12667,39 @@
       <c r="BO179" s="7"/>
       <c r="BP179" s="7"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="30" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="31" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="31" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="31" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="31" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="31" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="26" t="s">
         <v>50</v>
       </c>
@@ -12763,7 +12716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="26" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -12785,7 +12738,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="26" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -12807,7 +12760,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="26" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -12829,7 +12782,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="26" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -12851,7 +12804,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="26" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -12873,7 +12826,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="26" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -12895,7 +12848,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="26" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -12917,7 +12870,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="26" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -12939,7 +12892,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="26" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -12961,7 +12914,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="26" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -12983,7 +12936,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="26" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -13005,7 +12958,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="26" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -13027,7 +12980,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="26" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -13049,31 +13002,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="6" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="5" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="31" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="30" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="26" t="s">
         <v>3</v>
       </c>
@@ -13081,7 +13034,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="26" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -13091,7 +13044,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -13101,13 +13054,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="26" t="s">
         <v>55</v>
       </c>
@@ -13115,7 +13068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="26" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -13125,7 +13078,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -13135,7 +13088,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -13145,7 +13098,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -13155,7 +13108,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -13165,7 +13118,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -13175,7 +13128,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -13185,7 +13138,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -13195,7 +13148,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -13205,7 +13158,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -13215,7 +13168,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -13225,7 +13178,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -13235,25 +13188,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="6" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="5" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="31" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="26" t="s">
         <v>34</v>
       </c>
@@ -13303,7 +13256,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="26" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13369,7 +13322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13435,7 +13388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13501,7 +13454,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13567,7 +13520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13633,7 +13586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13699,7 +13652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13765,7 +13718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13831,7 +13784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13897,7 +13850,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13963,7 +13916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14029,7 +13982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14095,7 +14048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14161,7 +14114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14227,7 +14180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14293,7 +14246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -14359,7 +14312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -14425,7 +14378,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -14491,7 +14444,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -14557,31 +14510,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="6" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="5" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="30" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="26" t="s">
         <v>77</v>
       </c>
@@ -14589,7 +14542,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="26" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -14599,7 +14552,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -14609,17 +14562,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="26" t="s">
         <v>122</v>
       </c>
@@ -14630,7 +14583,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="26" t="s">
         <v>161</v>
       </c>
@@ -14641,7 +14594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="26" t="s">
         <v>163</v>
       </c>
@@ -14652,7 +14605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="26" t="s">
         <v>165</v>
       </c>
@@ -14663,7 +14616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="26" t="s">
         <v>167</v>
       </c>
@@ -14674,7 +14627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="26" t="s">
         <v>169</v>
       </c>
@@ -14685,12 +14638,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="26" t="s">
         <v>122</v>
       </c>
@@ -14701,7 +14654,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="26" t="s">
         <v>172</v>
       </c>
@@ -14712,7 +14665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="26" t="s">
         <v>174</v>
       </c>
@@ -14723,7 +14676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="26" t="s">
         <v>176</v>
       </c>
@@ -14734,7 +14687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="26" t="s">
         <v>178</v>
       </c>
@@ -14745,7 +14698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="26" t="s">
         <v>180</v>
       </c>
@@ -14756,12 +14709,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="26" t="s">
         <v>122</v>
       </c>
@@ -14772,7 +14725,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="26" t="s">
         <v>183</v>
       </c>
@@ -14783,7 +14736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="26" t="s">
         <v>185</v>
       </c>
@@ -14794,7 +14747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="26" t="s">
         <v>187</v>
       </c>
@@ -14805,7 +14758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="26" t="s">
         <v>189</v>
       </c>
@@ -14816,7 +14769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="26" t="s">
         <v>191</v>
       </c>
@@ -14827,12 +14780,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="26" t="s">
         <v>122</v>
       </c>
@@ -14843,7 +14796,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="26" t="s">
         <v>194</v>
       </c>
@@ -14854,7 +14807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="26" t="s">
         <v>196</v>
       </c>
@@ -14865,7 +14818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="26" t="s">
         <v>198</v>
       </c>
@@ -14876,7 +14829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="26" t="s">
         <v>200</v>
       </c>
@@ -14887,7 +14840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="26" t="s">
         <v>202</v>
       </c>
